--- a/Cell data Sara DU145/2026_03_18/2026_03_18.xlsx
+++ b/Cell data Sara DU145/2026_03_18/2026_03_18.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\bhaan\Documents\#Master Degree\Thesis\Thesis_project\Cell data Sara DU145\2026_03_18\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A02ADC5B-86B6-4669-AB37-75EE0848AE30}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9270CB55-3218-44BB-A6BA-1EFC61AC436E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="52" uniqueCount="10">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="46" uniqueCount="11">
   <si>
     <t>Experiment</t>
   </si>
@@ -39,15 +39,6 @@
     <t>Cells plated</t>
   </si>
   <si>
-    <t>X-ray</t>
-  </si>
-  <si>
-    <t>Proton LL</t>
-  </si>
-  <si>
-    <t>Proton HL</t>
-  </si>
-  <si>
     <t>Rad</t>
   </si>
   <si>
@@ -55,6 +46,18 @@
   </si>
   <si>
     <t>Count</t>
+  </si>
+  <si>
+    <t>X</t>
+  </si>
+  <si>
+    <t>Proton L</t>
+  </si>
+  <si>
+    <t>Proton H</t>
+  </si>
+  <si>
+    <t>P</t>
   </si>
 </sst>
 </file>
@@ -861,12 +864,12 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:G46"/>
+  <dimension ref="A1:G40"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="B1" t="s">
         <v>0</v>
@@ -878,18 +881,18 @@
         <v>2</v>
       </c>
       <c r="E1" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="F1" t="s">
         <v>3</v>
       </c>
       <c r="G1" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="B2">
         <v>7</v>
@@ -912,7 +915,7 @@
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="B3">
         <v>7</v>
@@ -935,7 +938,7 @@
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="B4">
         <v>7</v>
@@ -958,7 +961,7 @@
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="B5">
         <v>7</v>
@@ -981,7 +984,7 @@
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="B6">
         <v>7</v>
@@ -1004,7 +1007,7 @@
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="B7">
         <v>7</v>
@@ -1027,7 +1030,7 @@
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="B8">
         <v>7</v>
@@ -1050,7 +1053,7 @@
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="B9">
         <v>7</v>
@@ -1073,7 +1076,7 @@
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="B10">
         <v>7</v>
@@ -1096,7 +1099,7 @@
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="B11">
         <v>7</v>
@@ -1119,7 +1122,7 @@
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="B12">
         <v>7</v>
@@ -1142,7 +1145,7 @@
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="B13">
         <v>7</v>
@@ -1165,7 +1168,7 @@
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="B14">
         <v>7</v>
@@ -1188,7 +1191,7 @@
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="B15">
         <v>7</v>
@@ -1211,7 +1214,7 @@
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="B16">
         <v>7</v>
@@ -1234,7 +1237,7 @@
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="B17">
         <v>7</v>
@@ -1257,7 +1260,7 @@
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="B18">
         <v>7</v>
@@ -1280,7 +1283,7 @@
     </row>
     <row r="19" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="B19">
         <v>7</v>
@@ -1303,7 +1306,7 @@
     </row>
     <row r="20" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="B20">
         <v>7</v>
@@ -1326,7 +1329,7 @@
     </row>
     <row r="21" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="B21">
         <v>7</v>
@@ -1349,7 +1352,7 @@
     </row>
     <row r="22" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="B22">
         <v>7</v>
@@ -1372,7 +1375,7 @@
     </row>
     <row r="23" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="B23">
         <v>7</v>
@@ -1395,7 +1398,7 @@
     </row>
     <row r="24" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="B24">
         <v>7</v>
@@ -1418,7 +1421,7 @@
     </row>
     <row r="25" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="B25">
         <v>7</v>
@@ -1441,7 +1444,7 @@
     </row>
     <row r="26" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="B26">
         <v>7</v>
@@ -1464,7 +1467,7 @@
     </row>
     <row r="27" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="B27">
         <v>7</v>
@@ -1487,7 +1490,7 @@
     </row>
     <row r="28" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="B28">
         <v>7</v>
@@ -1510,7 +1513,7 @@
     </row>
     <row r="29" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="B29">
         <v>7</v>
@@ -1533,7 +1536,7 @@
     </row>
     <row r="30" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="B30">
         <v>7</v>
@@ -1556,7 +1559,7 @@
     </row>
     <row r="31" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="B31">
         <v>7</v>
@@ -1579,7 +1582,7 @@
     </row>
     <row r="32" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="B32">
         <v>7</v>
@@ -1588,21 +1591,21 @@
         <v>16.5</v>
       </c>
       <c r="D32">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E32">
         <v>1</v>
       </c>
       <c r="F32">
-        <v>250</v>
+        <v>500</v>
       </c>
       <c r="G32">
-        <v>69</v>
+        <v>24</v>
       </c>
     </row>
     <row r="33" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A33" t="s">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="B33">
         <v>7</v>
@@ -1611,21 +1614,21 @@
         <v>16.5</v>
       </c>
       <c r="D33">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E33">
         <v>2</v>
       </c>
       <c r="F33">
-        <v>250</v>
+        <v>500</v>
       </c>
       <c r="G33">
-        <v>96</v>
+        <v>33</v>
       </c>
     </row>
     <row r="34" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A34" t="s">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="B34">
         <v>7</v>
@@ -1634,21 +1637,21 @@
         <v>16.5</v>
       </c>
       <c r="D34">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E34">
         <v>3</v>
       </c>
       <c r="F34">
-        <v>250</v>
+        <v>500</v>
       </c>
       <c r="G34">
-        <v>85</v>
+        <v>44</v>
       </c>
     </row>
     <row r="35" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A35" t="s">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="B35">
         <v>7</v>
@@ -1657,21 +1660,21 @@
         <v>16.5</v>
       </c>
       <c r="D35">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="E35">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F35">
-        <v>250</v>
+        <v>2000</v>
       </c>
       <c r="G35">
-        <v>82</v>
+        <v>11</v>
       </c>
     </row>
     <row r="36" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A36" t="s">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="B36">
         <v>7</v>
@@ -1680,21 +1683,21 @@
         <v>16.5</v>
       </c>
       <c r="D36">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="E36">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="F36">
-        <v>250</v>
+        <v>2000</v>
       </c>
       <c r="G36">
-        <v>76</v>
+        <v>20</v>
       </c>
     </row>
     <row r="37" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A37" t="s">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="B37">
         <v>7</v>
@@ -1703,21 +1706,21 @@
         <v>16.5</v>
       </c>
       <c r="D37">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="E37">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="F37">
-        <v>250</v>
+        <v>2000</v>
       </c>
       <c r="G37">
-        <v>77</v>
+        <v>14</v>
       </c>
     </row>
     <row r="38" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A38" t="s">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="B38">
         <v>7</v>
@@ -1726,21 +1729,21 @@
         <v>16.5</v>
       </c>
       <c r="D38">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="E38">
         <v>1</v>
       </c>
       <c r="F38">
-        <v>500</v>
+        <v>5000</v>
       </c>
       <c r="G38">
-        <v>24</v>
+        <v>4</v>
       </c>
     </row>
     <row r="39" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A39" t="s">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="B39">
         <v>7</v>
@@ -1749,21 +1752,21 @@
         <v>16.5</v>
       </c>
       <c r="D39">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="E39">
         <v>2</v>
       </c>
       <c r="F39">
-        <v>500</v>
+        <v>5000</v>
       </c>
       <c r="G39">
-        <v>33</v>
+        <v>4</v>
       </c>
     </row>
     <row r="40" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A40" t="s">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="B40">
         <v>7</v>
@@ -1772,153 +1775,15 @@
         <v>16.5</v>
       </c>
       <c r="D40">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="E40">
         <v>3</v>
       </c>
       <c r="F40">
-        <v>500</v>
+        <v>5000</v>
       </c>
       <c r="G40">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="41" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A41" t="s">
-        <v>6</v>
-      </c>
-      <c r="B41">
-        <v>7</v>
-      </c>
-      <c r="C41">
-        <v>16.5</v>
-      </c>
-      <c r="D41">
-        <v>5</v>
-      </c>
-      <c r="E41">
-        <v>1</v>
-      </c>
-      <c r="F41">
-        <v>2000</v>
-      </c>
-      <c r="G41">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="42" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A42" t="s">
-        <v>6</v>
-      </c>
-      <c r="B42">
-        <v>7</v>
-      </c>
-      <c r="C42">
-        <v>16.5</v>
-      </c>
-      <c r="D42">
-        <v>5</v>
-      </c>
-      <c r="E42">
-        <v>2</v>
-      </c>
-      <c r="F42">
-        <v>2000</v>
-      </c>
-      <c r="G42">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="43" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A43" t="s">
-        <v>6</v>
-      </c>
-      <c r="B43">
-        <v>7</v>
-      </c>
-      <c r="C43">
-        <v>16.5</v>
-      </c>
-      <c r="D43">
-        <v>5</v>
-      </c>
-      <c r="E43">
-        <v>3</v>
-      </c>
-      <c r="F43">
-        <v>2000</v>
-      </c>
-      <c r="G43">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="44" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A44" t="s">
-        <v>6</v>
-      </c>
-      <c r="B44">
-        <v>7</v>
-      </c>
-      <c r="C44">
-        <v>16.5</v>
-      </c>
-      <c r="D44">
-        <v>8</v>
-      </c>
-      <c r="E44">
-        <v>1</v>
-      </c>
-      <c r="F44">
-        <v>5000</v>
-      </c>
-      <c r="G44">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="45" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A45" t="s">
-        <v>6</v>
-      </c>
-      <c r="B45">
-        <v>7</v>
-      </c>
-      <c r="C45">
-        <v>16.5</v>
-      </c>
-      <c r="D45">
-        <v>8</v>
-      </c>
-      <c r="E45">
-        <v>2</v>
-      </c>
-      <c r="F45">
-        <v>5000</v>
-      </c>
-      <c r="G45">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="46" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A46" t="s">
-        <v>6</v>
-      </c>
-      <c r="B46">
-        <v>7</v>
-      </c>
-      <c r="C46">
-        <v>16.5</v>
-      </c>
-      <c r="D46">
-        <v>8</v>
-      </c>
-      <c r="E46">
-        <v>3</v>
-      </c>
-      <c r="F46">
-        <v>5000</v>
-      </c>
-      <c r="G46">
         <v>5</v>
       </c>
     </row>

--- a/Cell data Sara DU145/2026_03_18/2026_03_18.xlsx
+++ b/Cell data Sara DU145/2026_03_18/2026_03_18.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\bhaan\Documents\#Master Degree\Thesis\Thesis_project\Cell data Sara DU145\2026_03_18\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9270CB55-3218-44BB-A6BA-1EFC61AC436E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FD02AC95-5072-4D61-A50D-A324E94941C5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1039,7 +1039,7 @@
         <v>2</v>
       </c>
       <c r="D8">
-        <v>1.7</v>
+        <v>2</v>
       </c>
       <c r="E8">
         <v>1</v>
@@ -1062,7 +1062,7 @@
         <v>2</v>
       </c>
       <c r="D9">
-        <v>1.7</v>
+        <v>2</v>
       </c>
       <c r="E9">
         <v>2</v>
@@ -1085,7 +1085,7 @@
         <v>2</v>
       </c>
       <c r="D10">
-        <v>1.7</v>
+        <v>2</v>
       </c>
       <c r="E10">
         <v>3</v>
@@ -1108,7 +1108,7 @@
         <v>2</v>
       </c>
       <c r="D11">
-        <v>4.25</v>
+        <v>5</v>
       </c>
       <c r="E11">
         <v>1</v>
@@ -1131,7 +1131,7 @@
         <v>2</v>
       </c>
       <c r="D12">
-        <v>4.25</v>
+        <v>5</v>
       </c>
       <c r="E12">
         <v>2</v>
@@ -1154,7 +1154,7 @@
         <v>2</v>
       </c>
       <c r="D13">
-        <v>4.25</v>
+        <v>5</v>
       </c>
       <c r="E13">
         <v>3</v>
@@ -1177,7 +1177,7 @@
         <v>2</v>
       </c>
       <c r="D14">
-        <v>6.8</v>
+        <v>8</v>
       </c>
       <c r="E14">
         <v>1</v>
@@ -1200,7 +1200,7 @@
         <v>2</v>
       </c>
       <c r="D15">
-        <v>6.8</v>
+        <v>8</v>
       </c>
       <c r="E15">
         <v>2</v>
@@ -1223,7 +1223,7 @@
         <v>2</v>
       </c>
       <c r="D16">
-        <v>6.8</v>
+        <v>8</v>
       </c>
       <c r="E16">
         <v>3</v>
